--- a/Excel/IED_PIB_6.xlsx
+++ b/Excel/IED_PIB_6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpresearchcr-my.sharepoint.com/personal/jcornick_drpresearch_com/Documents/RstudioDRP/NSMX_C2/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonathan.barboza\Documents\Temas DGIE\Materiales reporte trimestral\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA7FECAE-2265-4C97-AE5B-45AC8E178E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BB2D8D-9A89-4A12-A35F-D8597CBC7911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4748" yWindow="3728" windowWidth="21600" windowHeight="11332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IED_PIB_Trimestral" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,8 @@
     <sheet name="Metodología" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_ftn1" localSheetId="2">Metodología!$A$28</definedName>
-    <definedName name="_ftn2" localSheetId="2">Metodología!$A$29</definedName>
-    <definedName name="_ftnref1" localSheetId="2">Metodología!$A$2</definedName>
-    <definedName name="_ftnref2" localSheetId="2">Metodología!$A$12</definedName>
     <definedName name="A">#N/A</definedName>
     <definedName name="A_impresión_IM" localSheetId="1">#REF!</definedName>
-    <definedName name="A_impresión_IM" localSheetId="2">#REF!</definedName>
     <definedName name="A_impresión_IM">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="17">
   <si>
     <t>Año</t>
   </si>
@@ -77,25 +72,25 @@
     <t>IV</t>
   </si>
   <si>
-    <t>Fuente: Secretaría de Economía, INEGI y Banco de México.</t>
-  </si>
-  <si>
-    <t>FLUJOS DE IED COMO PORCENTAJE DEL PRODUCTO INTERNO BRUTO TRIMESTRAL ANUALIZADO*/</t>
-  </si>
-  <si>
-    <t>FLUJOS DE IED COMO PORCENTAJE DEL PRODUCTO INTERNO BRUTO ANUAL EN SU FORMA ANUALIZADA*/</t>
-  </si>
-  <si>
     <t>Millones de dólares corrientes</t>
   </si>
   <si>
-    <t>*/ Con información al 31 de diciembre de 2025.</t>
+    <t>Nota metodológica 2: Los flujos de IED previos al año 2006 no se encuentran sujetos a nuevas actualizaciones.</t>
   </si>
   <si>
-    <t>Nota metodológica: Las cifras referentes a la IED y al PIB se presentan en dólares. La Secretaría de Economía realiza la conversión del PIB trimestral utilizando el tipo de cambio FIX publicado por el Banco de México, en promedio por cada trimestre. Asimismo, el PIB trimestral se presenta anualizada en la fuente original, por lo cual se desanualiza para dimesionar la participación del flujo trimestral de la IED.</t>
+    <t>Fuente: Secretaría de Economía, INEGI y Banco de México. Información actualizada al 30 de junio de 2026.</t>
   </si>
   <si>
-    <t>Nota metodológica: Las cifras referentes a la IED y al PIB se presentan en dólares. La Secretaría de Economía realiza el calculo del PIB a partir del promedio simple del PIB trimestral anualizada, expresada en dólares americanos utilizando el tipo de cambio FIX publicado por el Banco de México.</t>
+    <t>FLUJOS DE IED COMO PORCENTAJE DEL PRODUCTO INTERNO BRUTO TRIMESTRAL ANUALIZADO</t>
+  </si>
+  <si>
+    <t>FLUJOS DE IED COMO PORCENTAJE DEL PRODUCTO INTERNO BRUTO ANUAL</t>
+  </si>
+  <si>
+    <t>Nota metodológica 1:  Las cifras referentes a la IED y al PIB se expresan en dólares corrientes, para lo cual la Secretaría de Economía realiza la conversión del PIB utilizando el promedio anual del tipo de cambio FIX.</t>
+  </si>
+  <si>
+    <t>Nota metodológica 1:  Las cifras referentes a la IED y al PIB se expresan en dólares corrientes, para lo cual la Secretaría de Economía realiza la conversión del PIB utilizando el promedio trimestral del tipo de cambio FIX. Asimismo, los datos del PIB anualizado presentados por el INEGI se dividieron entre cuatro para expresarlos en niveles trimestrales, con lo cual se facilita la comparación con los flujos trimestrales de IED.</t>
   </si>
 </sst>
 </file>
@@ -106,7 +101,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -170,6 +165,12 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -304,15 +305,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -473,12 +465,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -549,17 +551,16 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -587,7 +588,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -597,96 +598,103 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -709,7 +717,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -782,11 +790,11 @@
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
-              <c:idx val="4"/>
+              <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.9633744995440961E-3"/>
-                  <c:y val="-6.0102218056602136E-17"/>
+                  <c:x val="-7.8003120124804995E-4"/>
+                  <c:y val="5.0734403798181919E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -798,7 +806,35 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-FEFE-464F-96D4-ADC4FC6C04ED}"/>
+                  <c16:uniqueId val="{00000002-EBD5-435D-9183-72FE9AC0FAF8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="5.0735069604006663E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="1.7074882995319812E-2"/>
+                      <c:h val="3.0761960169631342E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-EBD5-435D-9183-72FE9AC0FAF8}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -806,8 +842,8 @@
               <c:idx val="5"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="2.2225308746580672E-3"/>
-                  <c:y val="8.1958516858027363E-3"/>
+                  <c:x val="0"/>
+                  <c:y val="-8.4557339663638188E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -819,16 +855,44 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-FEFE-464F-96D4-ADC4FC6C04ED}"/>
+                  <c16:uniqueId val="{00000003-EBD5-435D-9183-72FE9AC0FAF8}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="34"/>
+              <c:idx val="11"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.2225308746581214E-3"/>
-                  <c:y val="8.1958516858027363E-3"/>
+                  <c:x val="1.430040682336099E-17"/>
+                  <c:y val="8.4558005469461059E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="1.670046801872075E-2"/>
+                      <c:h val="3.2453106962904092E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-EBD5-435D-9183-72FE9AC0FAF8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.5600624024961142E-3"/>
+                  <c:y val="-1.0146880759636569E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -840,16 +904,38 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-FEFE-464F-96D4-ADC4FC6C04ED}"/>
+                  <c16:uniqueId val="{00000006-EBD5-435D-9183-72FE9AC0FAF8}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="35"/>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="1.8978159126365055E-2"/>
+                      <c:h val="4.4291134515813346E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-EBD5-435D-9183-72FE9AC0FAF8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0"/>
-                  <c:y val="8.195851685802797E-3"/>
+                  <c:x val="5.4602184087363496E-3"/>
+                  <c:y val="5.0734403798182535E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -861,49 +947,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-FEFE-464F-96D4-ADC4FC6C04ED}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="44"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-7.4084362488602241E-4"/>
-                  <c:y val="8.1958516858027363E-3"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-052B-421F-9A92-2764B71C3D7C}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="45"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="3.7042181244300574E-3"/>
-                  <c:y val="8.195851685802797E-3"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-052B-421F-9A92-2764B71C3D7C}"/>
+                  <c16:uniqueId val="{00000008-EBD5-435D-9183-72FE9AC0FAF8}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -982,9 +1026,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>IED_PIB_Trimestral!$A$8:$B$115</c:f>
+              <c:f>IED_PIB_Trimestral!$A$8:$B$117</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="108"/>
+                <c:ptCount val="110"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>I</c:v>
@@ -1309,6 +1353,12 @@
                   </c:pt>
                   <c:pt idx="107">
                     <c:v>IV</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>I</c:v>
+                  </c:pt>
+                  <c:pt idx="109">
+                    <c:v>II</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1392,6 +1442,9 @@
                   </c:pt>
                   <c:pt idx="104">
                     <c:v>2025</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>2026</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1399,10 +1452,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IED_PIB_Trimestral!$E$8:$E$115</c:f>
+              <c:f>IED_PIB_Trimestral!$E$8:$E$117</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2.5258593295886596</c:v>
                 </c:pt>
@@ -1488,244 +1541,250 @@
                   <c:v>2.7863657970806499</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.9883739077558227</c:v>
+                  <c:v>2.9883739077558524</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.6433795221505445</c:v>
+                  <c:v>2.643379522150525</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.91356837276417391</c:v>
+                  <c:v>0.91356837276415792</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.8318474431681528</c:v>
+                  <c:v>1.8318492241796689</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4.1715025067917333</c:v>
+                  <c:v>4.1715025067917155</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.2204616494649341</c:v>
+                  <c:v>2.2204616494649136</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.7577269434835365</c:v>
+                  <c:v>2.7577277681362133</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2.6900780231174339</c:v>
+                  <c:v>2.6900780231174157</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>3.0075200818750836</c:v>
+                  <c:v>3.0075200818750663</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.6362435657108847</c:v>
+                  <c:v>2.6364975231188659</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.7730846020731008</c:v>
+                  <c:v>1.7730846020730786</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.7828624268813886</c:v>
+                  <c:v>2.7828640005480829</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.8852047265250529</c:v>
+                  <c:v>2.8852047265250342</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.6035241387767836</c:v>
+                  <c:v>2.6035241387767591</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.98725545147189431</c:v>
+                  <c:v>0.9872555849652489</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.2623824809698159</c:v>
+                  <c:v>1.2623824809698048</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3.3333286530724786</c:v>
+                  <c:v>3.3333286530724835</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3.3775401289060367</c:v>
+                  <c:v>3.3775401289060425</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.4366987361327264</c:v>
+                  <c:v>1.4366987361327195</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.7736543735798556</c:v>
+                  <c:v>1.7736546472646577</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2.8077110938985834</c:v>
+                  <c:v>2.8077125407813472</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2.1050221793667707</c:v>
+                  <c:v>2.1050234918346682</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.3965944560278336</c:v>
+                  <c:v>1.3965958434817967</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2.0565552014020865</c:v>
+                  <c:v>2.0565555202727794</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.5478012207332523</c:v>
+                  <c:v>2.5479611622380771</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.8622898419058689</c:v>
+                  <c:v>1.8622898419058727</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.8225696077024438</c:v>
+                  <c:v>1.8226655920882531</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.7648295107672205</c:v>
+                  <c:v>0.76482951090181506</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>3.2586207446637503</c:v>
+                  <c:v>3.2586207452590963</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>6.2279120498550986</c:v>
+                  <c:v>6.2279120505944876</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.2710058259046901</c:v>
+                  <c:v>1.2711106188664716</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>3.7332160498972096</c:v>
+                  <c:v>3.7332171859936842</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>4.2051824314958184</c:v>
+                  <c:v>4.2051847028638871</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1.5785984717337178</c:v>
+                  <c:v>1.5788588379882909</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.92797177696622968</c:v>
+                  <c:v>0.92797177660970176</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2.2973893025055725</c:v>
+                  <c:v>2.2973895205193782</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>3.9461340372181639</c:v>
+                  <c:v>3.9461341186452406</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2.1385138807757871</c:v>
+                  <c:v>2.1385138906350658</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>3.2527192198171804</c:v>
+                  <c:v>3.2528135449900213</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>2.5234061795955798</c:v>
+                  <c:v>2.5234583314043357</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>4.7352037364967261</c:v>
+                  <c:v>4.7352121465196992</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>2.188285371155982</c:v>
+                  <c:v>2.1882941149512702</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1.548450971766242</c:v>
+                  <c:v>1.5484516027776396</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2.831843721828796</c:v>
+                  <c:v>2.8318440270721692</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>5.1108548975262238</c:v>
+                  <c:v>5.1167716616752736</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>2.2690731542902314</c:v>
+                  <c:v>2.2692636538135913</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2.0224787220444509</c:v>
+                  <c:v>2.0244547770647765</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>2.2848232829078423</c:v>
+                  <c:v>2.2848238893815753</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>4.5506378635995981</c:v>
+                  <c:v>4.5506462646607009</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>3.0845985212547342</c:v>
+                  <c:v>3.084601089962145</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>1.2918882360039838</c:v>
+                  <c:v>1.2918919868505967</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>1.9945104304954209</c:v>
+                  <c:v>1.9955085047289538</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>4.7611120116757428</c:v>
+                  <c:v>4.7611175470589213</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>1.9883347507070925</c:v>
+                  <c:v>2.0421176493807094</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>2.536631234263548</c:v>
+                  <c:v>2.5366429919517319</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>1.4018853781978518</c:v>
+                  <c:v>1.4027024763569054</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>5.3078906823695435</c:v>
+                  <c:v>5.3082258355420384</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>3.2764061775292319</c:v>
+                  <c:v>3.3054501342624234</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.48745792839796892</c:v>
+                  <c:v>0.48802543309868107</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.88104541895414368</c:v>
+                  <c:v>0.88151260235068918</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>5.2324209427830599</c:v>
+                  <c:v>5.2324474554884013</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1.7803824401747561</c:v>
+                  <c:v>1.7803954008182521</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1.9368027402540031</c:v>
+                  <c:v>1.9389708872755631</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>1.485800885768646</c:v>
+                  <c:v>1.4860305043042599</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>6.6875232003286005</c:v>
+                  <c:v>6.6874852216470684</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>2.2866309624842849</c:v>
+                  <c:v>2.2866325784934012</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.93895458497102147</c:v>
+                  <c:v>0.93921311594469292</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.4565499215000578</c:v>
+                  <c:v>0.4565676129261082</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>5.7851225366248027</c:v>
+                  <c:v>5.7855302496958156</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>1.9296932630868604</c:v>
+                  <c:v>1.9299209714391505</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.61879252749621139</c:v>
+                  <c:v>0.61878438656212398</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.26708633770122814</c:v>
+                  <c:v>0.27348133388109735</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>5.7883552443773576</c:v>
+                  <c:v>5.7806012549051804</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>1.333810889414822</c:v>
+                  <c:v>1.3330663519708192</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.68597743209787754</c:v>
+                  <c:v>0.686953111608406</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.27169622041337471</c:v>
+                  <c:v>0.27333991835686161</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>5.8258739760483911</c:v>
+                  <c:v>5.7291257627465182</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>3.0415403586652556</c:v>
+                  <c:v>3.0841330583184421</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>1.6359752296462458</c:v>
+                  <c:v>1.6689075661207551</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>-1.0136095694362115</c:v>
+                  <c:v>-0.80302712479043903</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5.6180779090793767</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.2217869031866713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1868,7 +1927,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2053,64 +2112,64 @@
                   <c:v>2.8076686627983372</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.0825406691781505</c:v>
+                  <c:v>2.0825411285283391</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.9376537344583227</c:v>
+                  <c:v>2.9376539413310283</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5229551482298338</c:v>
+                  <c:v>2.5230244480753523</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.8863984449962048</c:v>
+                  <c:v>1.8863984792611699</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.4581602842432453</c:v>
+                  <c:v>2.4581603572264314</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.0853794377680273</c:v>
+                  <c:v>2.0853805601826947</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.7336876459048312</c:v>
+                  <c:v>1.7337511638214218</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.6416896104932275</c:v>
+                  <c:v>3.6417158460376022</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.2257987894499753</c:v>
+                  <c:v>2.2258656611260852</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.9634975500966796</c:v>
+                  <c:v>2.9635334161424121</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.8084550908844728</c:v>
+                  <c:v>2.80845961080218</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.849623337240534</c:v>
+                  <c:v>2.8515272527319775</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.7140751428271201</c:v>
+                  <c:v>2.7143307072694003</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.6534755091269995</c:v>
+                  <c:v>2.6671780873772151</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.4978340450991543</c:v>
+                  <c:v>2.5039390775419332</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.572200397846518</c:v>
+                  <c:v>2.5728109893524209</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.4798568685526541</c:v>
+                  <c:v>2.4799343222518422</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.0268116573801271</c:v>
+                  <c:v>2.0282800228374396</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.0676354782208306</c:v>
+                  <c:v>2.0649107733313539</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.2217846152257978</c:v>
+                  <c:v>2.2756893390222515</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2156,7 +2215,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="800"/>
             </a:pPr>
             <a:endParaRPr lang="es-MX"/>
           </a:p>
@@ -2250,7 +2309,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>127374</xdr:rowOff>
+      <xdr:rowOff>134994</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
@@ -2286,7 +2345,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>773570</xdr:colOff>
+      <xdr:colOff>635000</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -2294,7 +2353,7 @@
       <xdr:col>23</xdr:col>
       <xdr:colOff>758907</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>252328</xdr:rowOff>
+      <xdr:rowOff>212604</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2324,8 +2383,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="17716164" y="0"/>
-          <a:ext cx="3509587" cy="800016"/>
+          <a:off x="16684625" y="0"/>
+          <a:ext cx="3457657" cy="752354"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2366,9 +2425,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>682067</xdr:colOff>
+      <xdr:colOff>583247</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>226432</xdr:rowOff>
+      <xdr:rowOff>213194</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2391,8 +2450,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20145375" y="47625"/>
-          <a:ext cx="3730067" cy="726495"/>
+          <a:off x="19109532" y="47625"/>
+          <a:ext cx="3432968" cy="697699"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2457,7 +2516,7 @@
               <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>, 1999 - 2025</a:t>
+            <a:t>, 1999 - 2026</a:t>
           </a:r>
         </a:p>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2557,15 +2616,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>388144</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>258574</xdr:rowOff>
+      <xdr:colOff>397669</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>16427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>483394</xdr:colOff>
+      <xdr:colOff>475774</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>183495</xdr:rowOff>
+      <xdr:rowOff>173970</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2595,15 +2654,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>168290</xdr:colOff>
+      <xdr:colOff>261055</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>57663</xdr:rowOff>
+      <xdr:rowOff>128219</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>457524</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>238124</xdr:rowOff>
+      <xdr:rowOff>248705</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2633,8 +2692,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11514946" y="57663"/>
-          <a:ext cx="3337234" cy="763867"/>
+          <a:off x="11091333" y="128219"/>
+          <a:ext cx="3103358" cy="691422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2674,8 +2733,8 @@
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>658255</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>20504</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>250031</xdr:rowOff>
     </xdr:to>
@@ -2870,22 +2929,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>210253</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>146943</xdr:rowOff>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2908,13 +2967,16 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="210253" y="299343"/>
-          <a:ext cx="6342947" cy="9320907"/>
+          <a:off x="142875" y="142875"/>
+          <a:ext cx="6581775" cy="9229725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
             <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2922,6 +2984,16 @@
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
           </a:ext>
         </a:extLst>
       </xdr:spPr>
@@ -3194,126 +3266,126 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD122"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="17.25" zeroHeight="1" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:AD125"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="19.8" zeroHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.84375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.53515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.3828125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="16" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.3046875" style="3" customWidth="1"/>
-    <col min="7" max="26" width="13.15234375" style="3" customWidth="1"/>
-    <col min="27" max="27" width="1.3046875" style="3" customWidth="1"/>
-    <col min="28" max="28" width="11.3828125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="2.25" style="3" customWidth="1"/>
+    <col min="7" max="26" width="13.125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="1.25" style="3" customWidth="1"/>
+    <col min="28" max="28" width="11.375" style="3" customWidth="1"/>
     <col min="29" max="29" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="4.3828125" style="3" customWidth="1"/>
-    <col min="31" max="16384" width="11.3828125" style="3" hidden="1"/>
+    <col min="30" max="30" width="4.375" style="3" customWidth="1"/>
+    <col min="31" max="16384" width="11.375" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="57" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="64"/>
-      <c r="Y1" s="64"/>
-      <c r="Z1" s="64"/>
-      <c r="AA1" s="64"/>
-      <c r="AB1" s="64"/>
-    </row>
-    <row r="2" spans="1:28" s="57" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="64"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="64"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="64"/>
-      <c r="U2" s="64"/>
-      <c r="V2" s="64"/>
-      <c r="W2" s="64"/>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="64"/>
-    </row>
-    <row r="3" spans="1:28" s="57" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="64"/>
-      <c r="Z3" s="64"/>
-      <c r="AA3" s="64"/>
-      <c r="AB3" s="64"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:28" s="56" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+    </row>
+    <row r="2" spans="1:28" s="56" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="62"/>
+    </row>
+    <row r="3" spans="1:28" s="56" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="62"/>
+      <c r="AB3" s="62"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:28" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="69" t="s">
+    <row r="6" spans="1:28" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="67" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -3326,19 +3398,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="70"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="71" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="72"/>
+    <row r="7" spans="1:28" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="68"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="70"/>
       <c r="E7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A8" s="73">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="71">
         <v>1999</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -3354,8 +3426,8 @@
         <v>2.5258593295886596</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A9" s="73"/>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="71"/>
       <c r="B9" s="9" t="s">
         <v>7</v>
       </c>
@@ -3369,8 +3441,8 @@
         <v>2.1630359205029945</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A10" s="73"/>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="71"/>
       <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
@@ -3384,8 +3456,8 @@
         <v>1.8414013868889092</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A11" s="73"/>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="71"/>
       <c r="B11" s="12" t="s">
         <v>9</v>
       </c>
@@ -3399,8 +3471,8 @@
         <v>2.3368699899245193</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A12" s="73">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="71">
         <v>2000</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -3416,8 +3488,8 @@
         <v>2.5735143431031307</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A13" s="73"/>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="71"/>
       <c r="B13" s="9" t="s">
         <v>7</v>
       </c>
@@ -3431,8 +3503,8 @@
         <v>2.6783228985009084</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A14" s="73"/>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="71"/>
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
@@ -3446,8 +3518,8 @@
         <v>1.5946137305904808</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A15" s="73"/>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="71"/>
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
@@ -3461,8 +3533,8 @@
         <v>3.0179774332746079</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.6">
-      <c r="A16" s="73">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="71">
         <v>2001</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -3478,8 +3550,8 @@
         <v>1.9064113223131018</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A17" s="73"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="71"/>
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -3493,8 +3565,8 @@
         <v>2.5684224566626055</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A18" s="73"/>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="71"/>
       <c r="B18" s="9" t="s">
         <v>8</v>
       </c>
@@ -3508,8 +3580,8 @@
         <v>8.0284711656228094</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A19" s="73"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="71"/>
       <c r="B19" s="12" t="s">
         <v>9</v>
       </c>
@@ -3523,8 +3595,8 @@
         <v>2.4403239428814305</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A20" s="73">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="71">
         <v>2002</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -3540,8 +3612,8 @@
         <v>2.5276616773789802</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A21" s="73"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="71"/>
       <c r="B21" s="9" t="s">
         <v>7</v>
       </c>
@@ -3555,8 +3627,8 @@
         <v>2.9863979526471334</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A22" s="73"/>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="71"/>
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -3570,8 +3642,8 @@
         <v>3.0343447115006796</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A23" s="73"/>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="71"/>
       <c r="B23" s="12" t="s">
         <v>9</v>
       </c>
@@ -3585,8 +3657,8 @@
         <v>3.3482929176462872</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A24" s="73">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="71">
         <v>2003</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -3602,8 +3674,8 @@
         <v>2.1185215489408944</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A25" s="73"/>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="71"/>
       <c r="B25" s="9" t="s">
         <v>7</v>
       </c>
@@ -3617,8 +3689,8 @@
         <v>2.8085064787757594</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A26" s="73"/>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="71"/>
       <c r="B26" s="9" t="s">
         <v>8</v>
       </c>
@@ -3632,8 +3704,8 @@
         <v>1.3159076150006999</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A27" s="73"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="71"/>
       <c r="B27" s="12" t="s">
         <v>9</v>
       </c>
@@ -3647,8 +3719,8 @@
         <v>3.2816480242761283</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A28" s="73">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="71">
         <v>2004</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -3664,8 +3736,8 @@
         <v>4.710004001023921</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A29" s="73"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="71"/>
       <c r="B29" s="9" t="s">
         <v>7</v>
       </c>
@@ -3679,8 +3751,8 @@
         <v>2.1366718600650829</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A30" s="73"/>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="71"/>
       <c r="B30" s="9" t="s">
         <v>8</v>
       </c>
@@ -3694,8 +3766,8 @@
         <v>1.6153017042884428</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A31" s="73"/>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="71"/>
       <c r="B31" s="12" t="s">
         <v>9</v>
       </c>
@@ -3709,8 +3781,8 @@
         <v>3.7540100148930762</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A32" s="73">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="71">
         <v>2005</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -3726,8 +3798,8 @@
         <v>3.2001518449239894</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A33" s="73"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="71"/>
       <c r="B33" s="9" t="s">
         <v>7</v>
       </c>
@@ -3741,8 +3813,8 @@
         <v>2.954135913271474</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A34" s="73"/>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="71"/>
       <c r="B34" s="9" t="s">
         <v>8</v>
       </c>
@@ -3756,8 +3828,8 @@
         <v>2.3335179427548693</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A35" s="73"/>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="71"/>
       <c r="B35" s="12" t="s">
         <v>9</v>
       </c>
@@ -3771,1387 +3843,1351 @@
         <v>2.7863657970806499</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A36" s="68">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="66">
         <v>2006</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="16">
-        <v>7437.8564357716077</v>
+        <v>7437.8564357716823</v>
       </c>
       <c r="D36" s="26">
         <v>248893.09923593901</v>
       </c>
       <c r="E36" s="17">
-        <f>C36/D36*100</f>
-        <v>2.9883739077558227</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A37" s="68"/>
+        <v>2.9883739077558524</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="66"/>
       <c r="B37" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="19">
-        <v>6634.3109912895179</v>
+        <v>6634.3109912894688</v>
       </c>
       <c r="D37" s="27">
         <v>250978.37581385652</v>
       </c>
       <c r="E37" s="20">
-        <f t="shared" ref="E37:E100" si="0">C37/D37*100</f>
-        <v>2.6433795221505445</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A38" s="68"/>
+        <v>2.643379522150525</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="66"/>
       <c r="B38" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="19">
-        <v>2346.7229354590299</v>
+        <v>2346.7229354589886</v>
       </c>
       <c r="D38" s="27">
         <v>256874.36271010299</v>
       </c>
       <c r="E38" s="20">
-        <f t="shared" si="0"/>
-        <v>0.91356837276417391</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A39" s="68"/>
+        <v>0.91356837276415792</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="66"/>
       <c r="B39" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="22">
-        <v>4817.9585849310697</v>
+        <v>4817.9632691856214</v>
       </c>
       <c r="D39" s="29">
         <v>263010.90753488085</v>
       </c>
       <c r="E39" s="20">
-        <f t="shared" si="0"/>
-        <v>1.8318474431681528</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A40" s="68">
+        <v>1.8318492241796689</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="66">
         <v>2007</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="16">
-        <v>10815.781410870057</v>
+        <v>10815.781410870009</v>
       </c>
       <c r="D40" s="26">
         <v>259277.83558227753</v>
       </c>
       <c r="E40" s="17">
-        <f t="shared" si="0"/>
-        <v>4.1715025067917333</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A41" s="68"/>
+        <v>4.1715025067917155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="66"/>
       <c r="B41" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="19">
-        <v>6137.6383039077155</v>
+        <v>6137.6383039076591</v>
       </c>
       <c r="D41" s="27">
         <v>276412.71378799563</v>
       </c>
       <c r="E41" s="20">
-        <f t="shared" si="0"/>
-        <v>2.2204616494649341</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A42" s="68"/>
+        <v>2.2204616494649136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="66"/>
       <c r="B42" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="19">
-        <v>7628.6535878138066</v>
+        <v>7628.6558690366146</v>
       </c>
       <c r="D42" s="27">
         <v>276628.31542623136</v>
       </c>
       <c r="E42" s="20">
-        <f t="shared" si="0"/>
-        <v>2.7577269434835365</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A43" s="68"/>
+        <v>2.7577277681362133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="66"/>
       <c r="B43" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="22">
-        <v>7811.9645158699423</v>
+        <v>7811.9645158698904</v>
       </c>
       <c r="D43" s="29">
         <v>290399.17982813524</v>
       </c>
       <c r="E43" s="23">
-        <f t="shared" si="0"/>
-        <v>2.6900780231174339</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A44" s="68">
+        <v>2.6900780231174157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="66">
         <v>2008</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="16">
-        <v>8554.8315152352734</v>
+        <v>8554.8315152352243</v>
       </c>
       <c r="D44" s="26">
         <v>284448.02635870135</v>
       </c>
       <c r="E44" s="17">
-        <f t="shared" si="0"/>
-        <v>3.0075200818750836</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A45" s="68"/>
+        <v>3.0075200818750663</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="66"/>
       <c r="B45" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="19">
-        <v>8376.7569183731575</v>
+        <v>8377.5638769948691</v>
       </c>
       <c r="D45" s="27">
         <v>317753.52730407886</v>
       </c>
       <c r="E45" s="20">
-        <f t="shared" si="0"/>
-        <v>2.6362435657108847</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A46" s="68"/>
+        <v>2.6364975231188659</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="66"/>
       <c r="B46" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="19">
-        <v>5644.1373640638449</v>
+        <v>5644.1373640637739</v>
       </c>
       <c r="D46" s="27">
         <v>318323.07141264924</v>
       </c>
       <c r="E46" s="20">
-        <f t="shared" si="0"/>
-        <v>1.7730846020731008</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A47" s="68"/>
+        <v>1.7730846020730786</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="66"/>
       <c r="B47" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="22">
-        <v>6945.6932731704892</v>
+        <v>6945.6972008551884</v>
       </c>
       <c r="D47" s="29">
         <v>249588.09339900329</v>
       </c>
       <c r="E47" s="23">
-        <f t="shared" si="0"/>
-        <v>2.7828624268813886</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A48" s="68">
+        <v>2.7828640005480829</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="66">
         <v>2009</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="16">
-        <v>6105.2954136300341</v>
+        <v>6105.2954136299941</v>
       </c>
       <c r="D48" s="26">
         <v>211607.00859461247</v>
       </c>
       <c r="E48" s="17">
-        <f t="shared" si="0"/>
-        <v>2.8852047265250529</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A49" s="68"/>
+        <v>2.8852047265250342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="66"/>
       <c r="B49" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="19">
-        <v>6094.493354614352</v>
+        <v>6094.4933546142947</v>
       </c>
       <c r="D49" s="27">
         <v>234086.30109639521</v>
       </c>
       <c r="E49" s="20">
-        <f t="shared" si="0"/>
-        <v>2.6035241387767836</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A50" s="68"/>
+        <v>2.6035241387767591</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="66"/>
       <c r="B50" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="19">
-        <v>2398.0365921942885</v>
+        <v>2398.0369164487138</v>
       </c>
       <c r="D50" s="27">
         <v>242899.30115038285</v>
       </c>
       <c r="E50" s="20">
-        <f t="shared" si="0"/>
-        <v>0.98725545147189431</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A51" s="68"/>
+        <v>0.9872555849652489</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="66"/>
       <c r="B51" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="22">
-        <v>3253.4346149189305</v>
+        <v>3253.4346149189023</v>
       </c>
       <c r="D51" s="29">
         <v>257721.78115300712</v>
       </c>
       <c r="E51" s="20">
-        <f t="shared" si="0"/>
-        <v>1.2623824809698159</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A52" s="68">
+        <v>1.2623824809698048</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="66">
         <v>2010</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="16">
-        <v>8722.7916987426652</v>
+        <v>8722.7916987426779</v>
       </c>
       <c r="D52" s="26">
         <v>261684.11838726062</v>
       </c>
       <c r="E52" s="17">
-        <f t="shared" si="0"/>
-        <v>3.3333286530724786</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A53" s="68"/>
+        <v>3.3333286530724835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="66"/>
       <c r="B53" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="19">
-        <v>9301.6213772700157</v>
+        <v>9301.6213772700303</v>
       </c>
       <c r="D53" s="27">
         <v>275396.3246110343</v>
       </c>
       <c r="E53" s="20">
-        <f t="shared" si="0"/>
-        <v>3.3775401289060367</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A54" s="68"/>
+        <v>3.3775401289060425</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="66"/>
       <c r="B54" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="19">
-        <v>3942.0841229426032</v>
+        <v>3942.0841229425846</v>
       </c>
       <c r="D54" s="27">
         <v>274384.88138117373</v>
       </c>
       <c r="E54" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4366987361327264</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A55" s="68"/>
+        <v>1.4366987361327195</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="66"/>
       <c r="B55" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C55" s="22">
-        <v>5232.5043760000099</v>
+        <v>5232.5051830468292</v>
       </c>
       <c r="D55" s="29">
-        <v>295012.62782325421</v>
+        <v>295012.62780307513</v>
       </c>
       <c r="E55" s="23">
-        <f t="shared" si="0"/>
-        <v>1.7736543735798556</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A56" s="68">
+        <v>1.7736546472646577</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="66">
         <v>2011</v>
       </c>
       <c r="B56" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C56" s="16">
-        <v>8431.2191248084346</v>
+        <v>8431.2234696236192</v>
       </c>
       <c r="D56" s="26">
-        <v>300287.98700586596</v>
+        <v>300287.98700586805</v>
       </c>
       <c r="E56" s="17">
-        <f t="shared" si="0"/>
-        <v>2.8077110938985834</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A57" s="68"/>
+        <v>2.8077125407813472</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="66"/>
       <c r="B57" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="19">
-        <v>6697.4453847119985</v>
+        <v>6697.4495600776772</v>
       </c>
       <c r="D57" s="27">
-        <v>318165.07447568618</v>
+        <v>318165.07445436652</v>
       </c>
       <c r="E57" s="20">
-        <f t="shared" si="0"/>
-        <v>2.1050221793667707</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A58" s="68"/>
+        <v>2.1050234918346682</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="66"/>
       <c r="B58" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="19">
-        <v>4349.890992388333</v>
+        <v>4349.8953138099669</v>
       </c>
       <c r="D58" s="27">
         <v>311464.14577358461</v>
       </c>
       <c r="E58" s="20">
-        <f t="shared" si="0"/>
-        <v>1.3965944560278336</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A59" s="68"/>
+        <v>1.3965958434817967</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="66"/>
       <c r="B59" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="22">
-        <v>6154.0092889798389</v>
+        <v>6154.0102435415483</v>
       </c>
       <c r="D59" s="29">
-        <v>299238.71164675051</v>
+        <v>299238.71166508971</v>
       </c>
       <c r="E59" s="23">
-        <f t="shared" si="0"/>
-        <v>2.0565552014020865</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A60" s="68">
+        <v>2.0565555202727794</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="66">
         <v>2012</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C60" s="16">
-        <v>7892.6936246853675</v>
+        <v>7893.1890991886285</v>
       </c>
       <c r="D60" s="26">
-        <v>309784.51381752087</v>
+        <v>309784.51383675769</v>
       </c>
       <c r="E60" s="17">
-        <f t="shared" si="0"/>
-        <v>2.5478012207332523</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A61" s="68"/>
+        <v>2.5479611622380771</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="66"/>
       <c r="B61" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="19">
-        <v>5622.1308966418583</v>
+        <v>5622.1308966418355</v>
       </c>
       <c r="D61" s="27">
-        <v>301893.44161852729</v>
+        <v>301893.44161852542</v>
       </c>
       <c r="E61" s="20">
-        <f t="shared" si="0"/>
-        <v>1.8622898419058689</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A62" s="68"/>
+        <v>1.8622898419058727</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="66"/>
       <c r="B62" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="19">
-        <v>5736.2922657135723</v>
+        <v>5736.5943636348911</v>
       </c>
       <c r="D62" s="27">
         <v>314736.5259176477</v>
       </c>
       <c r="E62" s="20">
-        <f t="shared" si="0"/>
-        <v>1.8225696077024438</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A63" s="68"/>
+        <v>1.8226655920882531</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="66"/>
       <c r="B63" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C63" s="22">
-        <v>2518.2153452201637</v>
+        <v>2518.2153452201601</v>
       </c>
       <c r="D63" s="29">
-        <v>329251.85414120281</v>
+        <v>329251.85408326064</v>
       </c>
       <c r="E63" s="23">
-        <f t="shared" si="0"/>
-        <v>0.7648295107672205</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A64" s="68">
+        <v>0.76482951090181506</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="66">
         <v>2013</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="16">
-        <v>10571.579649062274</v>
+        <v>10571.579649062236</v>
       </c>
       <c r="D64" s="26">
-        <v>324418.84089684486</v>
+        <v>324418.84083757282</v>
       </c>
       <c r="E64" s="17">
-        <f t="shared" si="0"/>
-        <v>3.2586207446637503</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A65" s="68"/>
+        <v>3.2586207452590963</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="66"/>
       <c r="B65" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="19">
-        <v>21019.149824980846</v>
+        <v>21019.149824980734</v>
       </c>
       <c r="D65" s="27">
-        <v>337499.14348051668</v>
+        <v>337499.14344044635</v>
       </c>
       <c r="E65" s="20">
-        <f t="shared" si="0"/>
-        <v>6.2279120498550986</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A66" s="68"/>
+        <v>6.2279120505944876</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="66"/>
       <c r="B66" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="19">
-        <v>4178.8102629067153</v>
+        <v>4179.1548007384272</v>
       </c>
       <c r="D66" s="27">
-        <v>328779.78823836445</v>
+        <v>328779.78821900173</v>
       </c>
       <c r="E66" s="20">
-        <f t="shared" si="0"/>
-        <v>1.2710058259046901</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A67" s="68"/>
+        <v>1.2711106188664716</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="66"/>
       <c r="B67" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C67" s="22">
-        <v>12587.220274832252</v>
+        <v>12587.224112553356</v>
       </c>
       <c r="D67" s="29">
-        <v>337168.27814395656</v>
+        <v>337168.27833586029</v>
       </c>
       <c r="E67" s="20">
-        <f t="shared" si="0"/>
-        <v>3.7332160498972096</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A68" s="68">
+        <v>3.7332171859936842</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="66">
         <v>2014</v>
       </c>
       <c r="B68" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C68" s="16">
-        <v>13828.000864523021</v>
+        <v>13828.008345434158</v>
       </c>
       <c r="D68" s="26">
-        <v>328832.36553436005</v>
+        <v>328832.36581776704</v>
       </c>
       <c r="E68" s="17">
-        <f t="shared" si="0"/>
-        <v>4.2051824314958184</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A69" s="68"/>
+        <v>4.2051847028638871</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="66"/>
       <c r="B69" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="19">
-        <v>5478.9218144462302</v>
+        <v>5479.8254865877934</v>
       </c>
       <c r="D69" s="27">
-        <v>347075.07403253263</v>
+        <v>347075.07439803384</v>
       </c>
       <c r="E69" s="20">
-        <f t="shared" si="0"/>
-        <v>1.5785984717337178</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A70" s="68"/>
+        <v>1.5788588379882909</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="66"/>
       <c r="B70" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="19">
-        <v>3222.1242099690189</v>
+        <v>3222.1242099690262</v>
       </c>
       <c r="D70" s="27">
-        <v>347222.22054025647</v>
+        <v>347222.22067366046</v>
       </c>
       <c r="E70" s="20">
-        <f t="shared" si="0"/>
-        <v>0.92797177696622968</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A71" s="65"/>
+        <v>0.92797177660970176</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="63"/>
       <c r="B71" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C71" s="22">
-        <v>7822.4502266866257</v>
+        <v>7822.4509491256849</v>
       </c>
       <c r="D71" s="29">
-        <v>340493.02041039919</v>
+        <v>340493.01954495028</v>
       </c>
       <c r="E71" s="23">
-        <f t="shared" si="0"/>
-        <v>2.2973893025055725</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A72" s="65">
+        <v>2.2973895205193782</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="63">
         <v>2015</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="24">
-        <v>12136.455959530873</v>
-      </c>
-      <c r="D72" s="61">
-        <v>307553.05940105609</v>
+        <v>12136.456160464986</v>
+      </c>
+      <c r="D72" s="58">
+        <v>307553.05814673094</v>
       </c>
       <c r="E72" s="17">
-        <f t="shared" si="0"/>
-        <v>3.9461340372181639</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A73" s="66"/>
+        <v>3.9461341186452406</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="64"/>
       <c r="B73" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C73" s="25">
-        <v>6656.8488480026253</v>
-      </c>
-      <c r="D73" s="34">
-        <v>311283.87371456879</v>
+        <v>6656.8488480026217</v>
+      </c>
+      <c r="D73" s="33">
+        <v>311283.87227944372</v>
       </c>
       <c r="E73" s="20">
-        <f t="shared" si="0"/>
-        <v>2.1385138807757871</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A74" s="66"/>
+        <v>2.1385138906350658</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="64"/>
       <c r="B74" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="25">
-        <v>9635.6377676483353</v>
-      </c>
-      <c r="D74" s="34">
-        <v>296233.30870193918</v>
+        <v>9635.9171847840498</v>
+      </c>
+      <c r="D74" s="33">
+        <v>296233.30853455386</v>
       </c>
       <c r="E74" s="20">
-        <f t="shared" si="0"/>
-        <v>3.2527192198171804</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A75" s="66"/>
+        <v>3.2528135449900213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="64"/>
       <c r="B75" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C75" s="25">
-        <v>7516.2303818237178</v>
-      </c>
-      <c r="D75" s="34">
-        <v>297860.50468610349</v>
+        <v>7516.3857907193606</v>
+      </c>
+      <c r="D75" s="33">
+        <v>297860.50743054668</v>
       </c>
       <c r="E75" s="23">
-        <f t="shared" si="0"/>
-        <v>2.5234061795955798</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A76" s="74">
+        <v>2.5234583314043357</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="72">
         <v>2016</v>
       </c>
       <c r="B76" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="16">
-        <v>12805.685004525179</v>
+        <v>12805.707928444443</v>
       </c>
       <c r="D76" s="26">
-        <v>270435.77672962571</v>
+        <v>270435.78053533297</v>
       </c>
       <c r="E76" s="17">
-        <f t="shared" si="0"/>
-        <v>4.7352037364967261</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A77" s="75"/>
+        <v>4.7352121465196992</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="73"/>
       <c r="B77" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C77" s="19">
-        <v>6210.7469518721646</v>
+        <v>6210.7718798170008</v>
       </c>
       <c r="D77" s="27">
-        <v>283817.96239817113</v>
+        <v>283817.96749269718</v>
       </c>
       <c r="E77" s="20">
-        <f t="shared" si="0"/>
-        <v>2.188285371155982</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A78" s="75"/>
+        <v>2.1882941149512702</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="73"/>
       <c r="B78" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="19">
-        <v>4320.0985201552676</v>
+        <v>4320.1002884910922</v>
       </c>
       <c r="D78" s="27">
-        <v>278994.8534972046</v>
+        <v>278994.85400393663</v>
       </c>
       <c r="E78" s="20">
-        <f t="shared" si="0"/>
-        <v>1.548450971766242</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A79" s="75"/>
+        <v>1.5484516027776396</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="73"/>
       <c r="B79" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C79" s="22">
-        <v>7855.7742798719855</v>
+        <v>7855.7748850580883</v>
       </c>
       <c r="D79" s="29">
-        <v>277408.46782317321</v>
+        <v>277408.45929216442</v>
       </c>
       <c r="E79" s="23">
-        <f t="shared" si="0"/>
-        <v>2.831843721828796</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A80" s="65">
+        <v>2.8318440270721692</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="63">
         <v>2017</v>
       </c>
       <c r="B80" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="16">
-        <v>13780.315352408652</v>
+        <v>13796.267995389069</v>
       </c>
       <c r="D80" s="26">
-        <v>269628.38172296097</v>
+        <v>269628.36936272541</v>
       </c>
       <c r="E80" s="17">
-        <f t="shared" si="0"/>
-        <v>5.1108548975262238</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A81" s="66"/>
+        <v>5.1167716616752736</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="64"/>
       <c r="B81" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="19">
-        <v>6837.3419401765786</v>
+        <v>6837.9154540115687</v>
       </c>
       <c r="D81" s="27">
-        <v>301327.52340967639</v>
+        <v>301327.50077410217</v>
       </c>
       <c r="E81" s="20">
-        <f t="shared" si="0"/>
-        <v>2.2690731542902314</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A82" s="66"/>
+        <v>2.2692636538135913</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="64"/>
       <c r="B82" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="19">
-        <v>6361.5013980808271</v>
+        <v>6367.7167730897245</v>
       </c>
       <c r="D82" s="27">
-        <v>314539.84305210464</v>
+        <v>314539.83784820186</v>
       </c>
       <c r="E82" s="20">
-        <f t="shared" si="0"/>
-        <v>2.0224787220444509</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A83" s="66"/>
+        <v>2.0244547770647765</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="64"/>
       <c r="B83" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C83" s="19">
-        <v>7062.6647916455304</v>
+        <v>7062.6675908012876</v>
       </c>
       <c r="D83" s="27">
-        <v>309112.08076700964</v>
+        <v>309112.12122842926</v>
       </c>
       <c r="E83" s="20">
-        <f t="shared" si="0"/>
-        <v>2.2848232829078423</v>
+        <v>2.2848238893815753</v>
       </c>
       <c r="G83" s="3"/>
     </row>
-    <row r="84" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A84" s="65">
+    <row r="84" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="63">
         <v>2018</v>
       </c>
       <c r="B84" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="16">
-        <v>14075.40459729129</v>
+        <v>14075.4335520269</v>
       </c>
       <c r="D84" s="26">
-        <v>309306.19001525006</v>
+        <v>309306.25527485099</v>
       </c>
       <c r="E84" s="17">
-        <f t="shared" si="0"/>
-        <v>4.5506378635995981</v>
+        <v>4.5506462646607009</v>
       </c>
       <c r="G84" s="3"/>
     </row>
-    <row r="85" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A85" s="66"/>
+    <row r="85" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="64"/>
       <c r="B85" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="19">
-        <v>9579.7159451963635</v>
+        <v>9579.7261917656724</v>
       </c>
       <c r="D85" s="27">
-        <v>310566.05516686774</v>
+        <v>310566.1287269803</v>
       </c>
       <c r="E85" s="20">
-        <f t="shared" si="0"/>
-        <v>3.0845985212547342</v>
+        <v>3.084601089962145</v>
       </c>
       <c r="G85" s="3"/>
     </row>
-    <row r="86" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A86" s="66"/>
+    <row r="86" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="64"/>
       <c r="B86" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="19">
-        <v>4133.5158426340558</v>
+        <v>4133.5281198081648</v>
       </c>
       <c r="D86" s="27">
-        <v>319959.24472690292</v>
+        <v>319959.26609042386</v>
       </c>
       <c r="E86" s="20">
-        <f t="shared" si="0"/>
-        <v>1.2918882360039838</v>
+        <v>1.2918919868505967</v>
       </c>
       <c r="G86" s="3"/>
     </row>
-    <row r="87" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A87" s="67"/>
+    <row r="87" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="65"/>
       <c r="B87" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C87" s="22">
-        <v>6322.2748553898646</v>
+        <v>6325.4355108148338</v>
       </c>
       <c r="D87" s="29">
-        <v>316983.79505688825</v>
+        <v>316983.64080257359</v>
       </c>
       <c r="E87" s="23">
-        <f t="shared" si="0"/>
-        <v>1.9945104304954209</v>
+        <v>1.9955085047289538</v>
       </c>
       <c r="G87" s="3"/>
     </row>
-    <row r="88" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A88" s="65">
+    <row r="88" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="63">
         <v>2019</v>
       </c>
       <c r="B88" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="16">
-        <v>15213.116431553977</v>
+        <v>15213.119239410031</v>
       </c>
       <c r="D88" s="26">
-        <v>319528.63940706779</v>
+        <v>319528.32689055556</v>
       </c>
       <c r="E88" s="17">
-        <f t="shared" si="0"/>
-        <v>4.7611120116757428</v>
+        <v>4.7611175470589213</v>
       </c>
       <c r="G88" s="3"/>
     </row>
-    <row r="89" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A89" s="66"/>
+    <row r="89" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="64"/>
       <c r="B89" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="19">
-        <v>6506.8206192988437</v>
+        <v>6682.8181742219622</v>
       </c>
       <c r="D89" s="27">
-        <v>327249.75595708343</v>
+        <v>327249.42053405137</v>
       </c>
       <c r="E89" s="20">
-        <f t="shared" si="0"/>
-        <v>1.9883347507070925</v>
+        <v>2.0421176493807094</v>
       </c>
       <c r="G89" s="3"/>
     </row>
-    <row r="90" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A90" s="66"/>
+    <row r="90" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="64"/>
       <c r="B90" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="19">
-        <v>8218.6973039439381</v>
+        <v>8218.7371136147758</v>
       </c>
       <c r="D90" s="27">
-        <v>324000.47720495902</v>
+        <v>324000.54480237101</v>
       </c>
       <c r="E90" s="20">
-        <f t="shared" si="0"/>
-        <v>2.536631234263548</v>
+        <v>2.5366429919517319</v>
       </c>
       <c r="G90" s="3"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A91" s="67"/>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="65"/>
       <c r="B91" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="22">
-        <v>4681.1140034669561</v>
+        <v>4683.8505065180452</v>
       </c>
       <c r="D91" s="29">
-        <v>333915.60225020751</v>
+        <v>333916.17862420314</v>
       </c>
       <c r="E91" s="23">
-        <f t="shared" si="0"/>
-        <v>1.4018853781978518</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A92" s="74">
+        <v>1.4027024763569054</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="72">
         <v>2020</v>
       </c>
       <c r="B92" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="16">
-        <v>16782.618658183317</v>
+        <v>16783.705275104265</v>
       </c>
       <c r="D92" s="26">
-        <v>316182.44727472868</v>
+        <v>316182.95443887101</v>
       </c>
       <c r="E92" s="17">
-        <f t="shared" si="0"/>
-        <v>5.3078906823695435</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A93" s="75"/>
+        <v>5.3082258355420384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="73"/>
       <c r="B93" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="19">
-        <v>7312.7951377603413</v>
+        <v>7377.6475508395852</v>
       </c>
       <c r="D93" s="27">
-        <v>223195.62171241501</v>
+        <v>223196.45588862681</v>
       </c>
       <c r="E93" s="20">
-        <f t="shared" si="0"/>
-        <v>3.2764061775292319</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A94" s="75"/>
+        <v>3.3054501342624234</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="73"/>
       <c r="B94" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="19">
-        <v>1337.7820705489009</v>
+        <v>1339.3389183585498</v>
       </c>
       <c r="D94" s="27">
-        <v>274440.51939939172</v>
+        <v>274440.39337345952</v>
       </c>
       <c r="E94" s="20">
-        <f t="shared" si="0"/>
-        <v>0.48745792839796892</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A95" s="76"/>
+        <v>0.48802543309868107</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="75"/>
       <c r="B95" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C95" s="22">
-        <v>2782.0905551690689</v>
+        <v>2783.5542884482593</v>
       </c>
       <c r="D95" s="29">
-        <v>315771.52497672429</v>
+        <v>315770.22053065186</v>
       </c>
       <c r="E95" s="23">
-        <f t="shared" si="0"/>
-        <v>0.88104541895414368</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A96" s="74">
+        <v>0.88151260235068918</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="72">
         <v>2021</v>
       </c>
       <c r="B96" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="16">
-        <v>16503.338739883602</v>
+        <v>16503.341052883206</v>
       </c>
       <c r="D96" s="26">
-        <v>315405.41023646464</v>
+        <v>315403.85628856299</v>
       </c>
       <c r="E96" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2324209427830599</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A97" s="75"/>
+        <v>5.2324474554884013</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="73"/>
       <c r="B97" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="19">
-        <v>5927.4183546739514</v>
+        <v>5927.4276814773821</v>
       </c>
       <c r="D97" s="27">
-        <v>332929.49991644133</v>
+        <v>332927.60016978224</v>
       </c>
       <c r="E97" s="20">
-        <f t="shared" si="0"/>
-        <v>1.7803824401747561</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A98" s="75"/>
+        <v>1.7803954008182521</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="73"/>
       <c r="B98" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="19">
-        <v>6432.6462084656587</v>
+        <v>6439.8444752176238</v>
       </c>
       <c r="D98" s="27">
-        <v>332127.07080443541</v>
+        <v>332126.92967588658</v>
       </c>
       <c r="E98" s="20">
-        <f t="shared" si="0"/>
-        <v>1.9368027402540031</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A99" s="76"/>
+        <v>1.9389708872755631</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="75"/>
       <c r="B99" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C99" s="22">
-        <v>4983.6119031798971</v>
+        <v>4984.4339488779478</v>
       </c>
       <c r="D99" s="29">
-        <v>335415.86567312729</v>
+        <v>335419.35609266616</v>
       </c>
       <c r="E99" s="23">
-        <f t="shared" si="0"/>
-        <v>1.485800885768646</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A100" s="74">
+        <v>1.4860305043042599</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="72">
         <v>2022</v>
       </c>
       <c r="B100" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="16">
-        <v>22783.230884297209</v>
+        <v>22783.259143496824</v>
       </c>
       <c r="D100" s="26">
-        <v>340682.64440828742</v>
+        <v>340685.0017365049</v>
       </c>
       <c r="E100" s="17">
-        <f t="shared" si="0"/>
-        <v>6.6875232003286005</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A101" s="75"/>
+        <v>6.6874852216470684</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="73"/>
       <c r="B101" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="19">
-        <v>8389.5554570227341</v>
+        <v>8389.640856693366</v>
       </c>
       <c r="D101" s="27">
-        <v>366895.90907611931</v>
+        <v>366899.3845185687</v>
       </c>
       <c r="E101" s="20">
-        <f t="shared" ref="E101:E114" si="1">C101/D101*100</f>
-        <v>2.2866309624842849</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A102" s="75"/>
+        <v>2.2866325784934012</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="73"/>
       <c r="B102" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C102" s="19">
-        <v>3449.3645464216743</v>
+        <v>3450.3624601140632</v>
       </c>
       <c r="D102" s="27">
-        <v>367362.23472705344</v>
+        <v>367367.3633319707</v>
       </c>
       <c r="E102" s="20">
-        <f t="shared" si="1"/>
-        <v>0.93895458497102147</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A103" s="75"/>
+        <v>0.93921311594469292</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="73"/>
       <c r="B103" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="19">
-        <v>1797.3013079805078</v>
+        <v>1797.3194814036085</v>
       </c>
       <c r="D103" s="27">
-        <v>393670.26985246787</v>
+        <v>393658.9960651655</v>
       </c>
       <c r="E103" s="23">
-        <f t="shared" si="1"/>
-        <v>0.4565499215000578</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A104" s="74">
+        <v>0.4565676129261082</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="72">
         <v>2023</v>
       </c>
       <c r="B104" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="16">
-        <v>23658.664414511535</v>
+        <v>23658.680795907672</v>
       </c>
       <c r="D104" s="26">
-        <v>408957.01456160756</v>
+        <v>408928.47802760289</v>
       </c>
       <c r="E104" s="17">
-        <f t="shared" si="1"/>
-        <v>5.7851225366248027</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A105" s="75"/>
+        <v>5.7855302496958156</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="73"/>
       <c r="B105" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C105" s="19">
-        <v>8644.3271284598413</v>
+        <v>8645.0936630379474</v>
       </c>
       <c r="D105" s="27">
-        <v>447963.79268235742</v>
+        <v>447950.65658006002</v>
       </c>
       <c r="E105" s="20">
-        <f t="shared" si="1"/>
-        <v>1.9296932630868604</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A106" s="75"/>
+        <v>1.9299209714391505</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="73"/>
       <c r="B106" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C106" s="19">
-        <v>2911.175633376753</v>
+        <v>2911.2510726828878</v>
       </c>
       <c r="D106" s="27">
-        <v>470460.69627829769</v>
+        <v>470479.07734992722</v>
       </c>
       <c r="E106" s="20">
-        <f t="shared" si="1"/>
-        <v>0.61879252749621139</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A107" s="76"/>
+        <v>0.61878438656212398</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="75"/>
       <c r="B107" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="22">
-        <v>1261.3670318179013</v>
+        <v>1292.3645450461595</v>
       </c>
       <c r="D107" s="29">
-        <v>472269.39523537492</v>
+        <v>472560.42184145784</v>
       </c>
       <c r="E107" s="23">
-        <f t="shared" si="1"/>
-        <v>0.26708633770122814</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A108" s="74">
+        <v>0.27348133388109735</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="72">
         <v>2024</v>
       </c>
       <c r="B108" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C108" s="16">
-        <v>27216.220855023865</v>
+        <v>27218.642307488983</v>
       </c>
       <c r="D108" s="26">
-        <v>470189.19375172973</v>
+        <v>470861.78594990209</v>
       </c>
       <c r="E108" s="17">
-        <f t="shared" si="1"/>
-        <v>5.7883552443773576</v>
-      </c>
-      <c r="G108" s="60"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A109" s="75"/>
+        <v>5.7806012549051804</v>
+      </c>
+      <c r="G108" s="57"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="73"/>
       <c r="B109" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="19">
-        <v>6481.5999923894906</v>
+        <v>6490.9179748317247</v>
       </c>
       <c r="D109" s="27">
-        <v>485945.94959658332</v>
+        <v>486916.34630455443</v>
       </c>
       <c r="E109" s="20">
-        <f t="shared" si="1"/>
-        <v>1.333810889414822</v>
-      </c>
-      <c r="G109" s="60"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A110" s="75"/>
+        <v>1.3330663519708192</v>
+      </c>
+      <c r="G109" s="57"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="73"/>
       <c r="B110" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C110" s="19">
-        <v>3063.0804967717627</v>
+        <v>3075.0483240757735</v>
       </c>
       <c r="D110" s="27">
-        <v>446527.88174155448</v>
+        <v>447635.83891133004</v>
       </c>
       <c r="E110" s="20">
-        <f t="shared" si="1"/>
-        <v>0.68597743209787754</v>
-      </c>
-      <c r="G110" s="60"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A111" s="75"/>
+        <v>0.686953111608406</v>
+      </c>
+      <c r="G110" s="57"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="73"/>
       <c r="B111" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="19">
-        <v>1173.8011058394311</v>
+        <v>1184.5630570115904</v>
       </c>
       <c r="D111" s="27">
-        <v>432027.02785248193</v>
+        <v>433366.28770960285</v>
       </c>
       <c r="E111" s="20">
-        <f t="shared" si="1"/>
-        <v>0.27169622041337471</v>
-      </c>
-      <c r="G111" s="60"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A112" s="77">
+        <v>0.27333991835686161</v>
+      </c>
+      <c r="G111" s="57"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="76">
         <v>2025</v>
       </c>
       <c r="B112" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C112" s="16">
-        <v>24411.733749407431</v>
+        <v>24061.155692803455</v>
       </c>
       <c r="D112" s="16">
-        <v>419022.6882656595</v>
+        <v>419979.53421201633</v>
       </c>
       <c r="E112" s="17">
-        <f t="shared" si="1"/>
-        <v>5.8258739760483911</v>
-      </c>
-      <c r="G112" s="60"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A113" s="78"/>
+        <v>5.7291257627465182</v>
+      </c>
+      <c r="G112" s="57"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="77"/>
       <c r="B113" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="19">
-        <v>13756.152285866512</v>
+        <v>13958.56480913311</v>
       </c>
       <c r="D113" s="19">
-        <v>452275.84262282279</v>
+        <v>452592.82090584381</v>
       </c>
       <c r="E113" s="20">
-        <f t="shared" si="1"/>
-        <v>3.0415403586652556</v>
-      </c>
-      <c r="G113" s="60"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A114" s="78"/>
+        <v>3.0841330583184421</v>
+      </c>
+      <c r="G113" s="57"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="77"/>
       <c r="B114" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C114" s="19">
-        <v>7728.6572601379657</v>
+        <v>7886.4657465510445</v>
       </c>
       <c r="D114" s="19">
-        <v>472418.96576937591</v>
+        <v>472552.57910313847</v>
       </c>
       <c r="E114" s="20">
-        <f t="shared" si="1"/>
-        <v>1.6359752296462458</v>
-      </c>
-      <c r="G114" s="60"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A115" s="79"/>
+        <v>1.6689075661207551</v>
+      </c>
+      <c r="G114" s="57"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="78"/>
       <c r="B115" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C115" s="22">
-        <v>-5025.7739673781398</v>
+        <v>-3989.5060849040219</v>
       </c>
       <c r="D115" s="22">
-        <v>495829.37246474187</v>
+        <v>496808.38439238752</v>
       </c>
       <c r="E115" s="23">
-        <f t="shared" ref="E115" si="2">C115/D115*100</f>
-        <v>-1.0136095694362115</v>
-      </c>
-      <c r="G115" s="60"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A116" s="32"/>
-      <c r="B116" s="33"/>
-      <c r="C116" s="34"/>
-      <c r="D116" s="34"/>
-      <c r="E116" s="35"/>
-    </row>
-    <row r="117" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A117" s="30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A118" s="31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A119" s="63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" s="63"/>
-      <c r="C119" s="63"/>
-      <c r="D119" s="63"/>
-      <c r="E119" s="63"/>
-      <c r="F119" s="63"/>
-      <c r="G119" s="63"/>
-      <c r="H119" s="63"/>
-      <c r="I119" s="63"/>
-      <c r="J119" s="63"/>
-      <c r="K119" s="63"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.6"/>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.6"/>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.6"/>
+        <v>-0.80302712479043903</v>
+      </c>
+      <c r="G115" s="57"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="79">
+        <v>2026</v>
+      </c>
+      <c r="B116" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="19">
+        <v>28367.342373115553</v>
+      </c>
+      <c r="D116" s="19">
+        <v>504929.67225091491</v>
+      </c>
+      <c r="E116" s="20">
+        <v>5.6180779090793767</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="80"/>
+      <c r="B117" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="22">
+        <v>6600.2042668907516</v>
+      </c>
+      <c r="D117" s="22">
+        <v>540209.11909237714</v>
+      </c>
+      <c r="E117" s="23">
+        <v>1.2217869031866713</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="31"/>
+      <c r="B118" s="32"/>
+      <c r="C118" s="33"/>
+      <c r="D118" s="33"/>
+      <c r="E118" s="34"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="31"/>
+      <c r="B119" s="32"/>
+      <c r="C119" s="33"/>
+      <c r="D119" s="33"/>
+      <c r="E119" s="34"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="B121" s="74"/>
+      <c r="C121" s="74"/>
+      <c r="D121" s="74"/>
+      <c r="E121" s="74"/>
+      <c r="F121" s="74"/>
+      <c r="G121" s="74"/>
+      <c r="H121" s="74"/>
+      <c r="I121" s="74"/>
+      <c r="J121" s="74"/>
+      <c r="K121" s="74"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="30"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="30"/>
+      <c r="E122" s="30"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A108:A111"/>
-    <mergeCell ref="A112:A115"/>
+  <mergeCells count="33">
+    <mergeCell ref="A121:K121"/>
     <mergeCell ref="A92:A95"/>
     <mergeCell ref="A96:A99"/>
     <mergeCell ref="A100:A103"/>
     <mergeCell ref="A88:A91"/>
     <mergeCell ref="A104:A107"/>
-    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A108:A111"/>
+    <mergeCell ref="A112:A115"/>
+    <mergeCell ref="A116:A117"/>
     <mergeCell ref="A72:A75"/>
     <mergeCell ref="A76:A79"/>
     <mergeCell ref="A80:A83"/>
@@ -5160,7 +5196,6 @@
     <mergeCell ref="A52:A55"/>
     <mergeCell ref="A56:A59"/>
     <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A119:K119"/>
     <mergeCell ref="A1:AB3"/>
     <mergeCell ref="A84:A87"/>
     <mergeCell ref="A40:A43"/>
@@ -5176,6 +5211,7 @@
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A68:A71"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5185,572 +5221,560 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W43"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:W44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.3828125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.53515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="3.3046875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.15234375" style="3" customWidth="1"/>
-    <col min="7" max="18" width="11.3828125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="4.69140625" style="3" customWidth="1"/>
-    <col min="20" max="20" width="11.3828125" style="3" customWidth="1"/>
-    <col min="21" max="22" width="10.3828125" style="3" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" style="3" customWidth="1"/>
-    <col min="24" max="16384" width="11.3828125" style="3" hidden="1"/>
+    <col min="1" max="1" width="11.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="3.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="3" customWidth="1"/>
+    <col min="7" max="18" width="11.375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="4.75" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11.375" style="3" customWidth="1"/>
+    <col min="21" max="22" width="10.375" style="3" customWidth="1"/>
+    <col min="23" max="23" width="6.25" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="11.375" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="36" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:22" s="35" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A1" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+    </row>
+    <row r="2" spans="1:22" s="35" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+    </row>
+    <row r="3" spans="1:22" s="35" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A3" s="84"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+    </row>
+    <row r="4" spans="1:22" s="35" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A4" s="36"/>
+    </row>
+    <row r="5" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="37"/>
+    </row>
+    <row r="7" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="82"/>
+      <c r="B7" s="83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="83"/>
+      <c r="D7" s="55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="45">
+        <v>1999</v>
+      </c>
+      <c r="B8" s="46">
+        <v>13960.317834420071</v>
+      </c>
+      <c r="C8" s="47">
+        <v>632428.64891098219</v>
+      </c>
+      <c r="D8" s="48">
+        <v>2.2074138890543922</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="49">
+        <v>2000</v>
+      </c>
+      <c r="B9" s="50">
+        <v>18248.688390210074</v>
+      </c>
+      <c r="C9" s="51">
+        <v>741818.03096676455</v>
+      </c>
+      <c r="D9" s="52">
+        <v>2.4599952587331568</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="49">
+        <v>2001</v>
+      </c>
+      <c r="B10" s="50">
+        <v>30057.181122777041</v>
+      </c>
+      <c r="C10" s="51">
+        <v>797004.66454347037</v>
+      </c>
+      <c r="D10" s="52">
+        <v>3.7712679059405501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="49">
+        <v>2002</v>
+      </c>
+      <c r="B11" s="50">
+        <v>24099.206211130102</v>
+      </c>
+      <c r="C11" s="51">
+        <v>810431.26933527819</v>
+      </c>
+      <c r="D11" s="52">
+        <v>2.973627391116886</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="49">
+        <v>2003</v>
+      </c>
+      <c r="B12" s="50">
+        <v>18249.968776300091</v>
+      </c>
+      <c r="C12" s="51">
+        <v>765701.80681885569</v>
+      </c>
+      <c r="D12" s="52">
+        <v>2.3834302875842015</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="49">
+        <v>2004</v>
+      </c>
+      <c r="B13" s="50">
+        <v>25015.569865094192</v>
+      </c>
+      <c r="C13" s="51">
+        <v>819342.97634619987</v>
+      </c>
+      <c r="D13" s="52">
+        <v>3.0531255636863199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="49">
+        <v>2005</v>
+      </c>
+      <c r="B14" s="50">
+        <v>25795.824800636266</v>
+      </c>
+      <c r="C14" s="51">
+        <v>918763.14117032429</v>
+      </c>
+      <c r="D14" s="52">
+        <v>2.8076686627983372</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="39">
+        <v>2006</v>
+      </c>
+      <c r="B15" s="40">
+        <v>21236.853631705759</v>
+      </c>
+      <c r="C15" s="41">
+        <v>1019756.7452947793</v>
+      </c>
+      <c r="D15" s="42">
+        <v>2.0825411285283391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="39">
+        <v>2007</v>
+      </c>
+      <c r="B16" s="40">
+        <v>32394.040099684174</v>
+      </c>
+      <c r="C16" s="41">
+        <v>1102718.0446246397</v>
+      </c>
+      <c r="D16" s="42">
+        <v>2.9376539413310283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="39">
+        <v>2008</v>
+      </c>
+      <c r="B17" s="40">
+        <v>29522.229957149058</v>
+      </c>
+      <c r="C17" s="41">
+        <v>1170112.7184744328</v>
+      </c>
+      <c r="D17" s="42">
+        <v>2.5230244480753523</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="39">
+        <v>2009</v>
+      </c>
+      <c r="B18" s="40">
+        <v>17851.260299611902</v>
+      </c>
+      <c r="C18" s="41">
+        <v>946314.39199439762</v>
+      </c>
+      <c r="D18" s="42">
+        <v>1.8863984792611699</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="39">
+        <v>2010</v>
+      </c>
+      <c r="B19" s="40">
+        <v>27199.002382002123</v>
+      </c>
+      <c r="C19" s="41">
+        <v>1106477.9521825439</v>
+      </c>
+      <c r="D19" s="42">
+        <v>2.4581603572264314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="39">
+        <v>2011</v>
+      </c>
+      <c r="B20" s="40">
+        <v>25632.578587052813</v>
+      </c>
+      <c r="C20" s="41">
+        <v>1229155.9188989089</v>
+      </c>
+      <c r="D20" s="42">
+        <v>2.0853805601826947</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="39">
+        <v>2012</v>
+      </c>
+      <c r="B21" s="40">
+        <v>21770.129704685518</v>
+      </c>
+      <c r="C21" s="41">
+        <v>1255666.3354561916</v>
+      </c>
+      <c r="D21" s="42">
+        <v>1.7337511638214218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="39">
+        <v>2013</v>
+      </c>
+      <c r="B22" s="40">
+        <v>48357.108387334752</v>
+      </c>
+      <c r="C22" s="41">
+        <v>1327866.0508328811</v>
+      </c>
+      <c r="D22" s="42">
+        <v>3.6417158460376022</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="39">
+        <v>2014</v>
+      </c>
+      <c r="B23" s="40">
+        <v>30352.408991116659</v>
+      </c>
+      <c r="C23" s="41">
+        <v>1363622.6804344116</v>
+      </c>
+      <c r="D23" s="42">
+        <v>2.2258656611260852</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="39">
+        <v>2015</v>
+      </c>
+      <c r="B24" s="40">
+        <v>35945.607983971015</v>
+      </c>
+      <c r="C24" s="41">
+        <v>1212930.7463912752</v>
+      </c>
+      <c r="D24" s="42">
+        <v>2.9635334161424121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="39">
+        <v>2016</v>
+      </c>
+      <c r="B25" s="40">
+        <v>31192.354981810626</v>
+      </c>
+      <c r="C25" s="41">
+        <v>1110657.0613241312</v>
+      </c>
+      <c r="D25" s="42">
+        <v>2.80845961080218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="39">
+        <v>2017</v>
+      </c>
+      <c r="B26" s="40">
+        <v>34064.567813291651</v>
+      </c>
+      <c r="C26" s="41">
+        <v>1194607.8292134586</v>
+      </c>
+      <c r="D26" s="42">
+        <v>2.8515272527319775</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="39">
+        <v>2018</v>
+      </c>
+      <c r="B27" s="40">
+        <v>34114.123374415576</v>
+      </c>
+      <c r="C27" s="41">
+        <v>1256815.2908948287</v>
+      </c>
+      <c r="D27" s="42">
+        <v>2.7143307072694003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="39">
+        <v>2019</v>
+      </c>
+      <c r="B28" s="40">
+        <v>34798.52503376481</v>
+      </c>
+      <c r="C28" s="41">
+        <v>1304694.4708511811</v>
+      </c>
+      <c r="D28" s="42">
+        <v>2.6671780873772151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="39">
+        <v>2020</v>
+      </c>
+      <c r="B29" s="40">
+        <v>28284.24603275066</v>
+      </c>
+      <c r="C29" s="41">
+        <v>1129590.0242316094</v>
+      </c>
+      <c r="D29" s="42">
+        <v>2.5039390775419332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="39">
+        <v>2021</v>
+      </c>
+      <c r="B30" s="40">
+        <v>33855.04715845616</v>
+      </c>
+      <c r="C30" s="41">
+        <v>1315877.7422268982</v>
+      </c>
+      <c r="D30" s="42">
+        <v>2.5728109893524209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="38">
+        <v>2022</v>
+      </c>
+      <c r="B31" s="40">
+        <v>36420.58194170786</v>
+      </c>
+      <c r="C31" s="41">
+        <v>1468610.74565221</v>
+      </c>
+      <c r="D31" s="42">
+        <v>2.4799343222518422</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="39">
+        <v>2023</v>
+      </c>
+      <c r="B32" s="40">
+        <v>36507.390076674666</v>
+      </c>
+      <c r="C32" s="41">
+        <v>1799918.6337990481</v>
+      </c>
+      <c r="D32" s="42">
+        <v>2.0282800228374396</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="60">
+        <v>2024</v>
+      </c>
+      <c r="B33" s="40">
+        <v>37969.171663408073</v>
+      </c>
+      <c r="C33" s="40">
+        <v>1838780.2588753894</v>
+      </c>
+      <c r="D33" s="42">
+        <v>2.0649107733313539</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="61">
+        <v>2025</v>
+      </c>
+      <c r="B34" s="43">
+        <v>41916.680163583587</v>
+      </c>
+      <c r="C34" s="43">
+        <v>1841933.318613386</v>
+      </c>
+      <c r="D34" s="59">
+        <v>2.2756893390222515</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="38" customFormat="1" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+    </row>
+    <row r="36" spans="1:11" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-    </row>
-    <row r="2" spans="1:22" s="36" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-    </row>
-    <row r="3" spans="1:22" s="36" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="83"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-    </row>
-    <row r="4" spans="1:22" s="36" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A4" s="37"/>
-    </row>
-    <row r="5" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-    </row>
-    <row r="6" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A6" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="38"/>
-    </row>
-    <row r="7" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A7" s="81"/>
-      <c r="B7" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="82"/>
-      <c r="D7" s="56" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A8" s="46">
-        <v>1999</v>
-      </c>
-      <c r="B8" s="47">
-        <v>13960.317834420071</v>
-      </c>
-      <c r="C8" s="48">
-        <v>632428.64891098265</v>
-      </c>
-      <c r="D8" s="49">
-        <v>2.2074138890543922</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A9" s="50">
-        <v>2000</v>
-      </c>
-      <c r="B9" s="51">
-        <v>18248.688390210074</v>
-      </c>
-      <c r="C9" s="52">
-        <v>741818.03096676478</v>
-      </c>
-      <c r="D9" s="53">
-        <v>2.4599952587331568</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A10" s="50">
-        <v>2001</v>
-      </c>
-      <c r="B10" s="51">
-        <v>30057.181122777041</v>
-      </c>
-      <c r="C10" s="52">
-        <v>797004.66454347037</v>
-      </c>
-      <c r="D10" s="53">
-        <v>3.7712679059405501</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A11" s="50">
-        <v>2002</v>
-      </c>
-      <c r="B11" s="51">
-        <v>24099.206211130102</v>
-      </c>
-      <c r="C11" s="52">
-        <v>810431.26933527843</v>
-      </c>
-      <c r="D11" s="53">
-        <v>2.973627391116886</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A12" s="50">
-        <v>2003</v>
-      </c>
-      <c r="B12" s="51">
-        <v>18249.968776300091</v>
-      </c>
-      <c r="C12" s="52">
-        <v>765701.80681885616</v>
-      </c>
-      <c r="D12" s="53">
-        <v>2.3834302875842015</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A13" s="50">
-        <v>2004</v>
-      </c>
-      <c r="B13" s="51">
-        <v>25015.569865094192</v>
-      </c>
-      <c r="C13" s="52">
-        <v>819342.9763462001</v>
-      </c>
-      <c r="D13" s="53">
-        <v>3.0531255636863199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A14" s="50">
-        <v>2005</v>
-      </c>
-      <c r="B14" s="51">
-        <v>25795.824800636266</v>
-      </c>
-      <c r="C14" s="52">
-        <v>918763.14119366836</v>
-      </c>
-      <c r="D14" s="53">
-        <v>2.8076686627983372</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A15" s="40">
-        <v>2006</v>
-      </c>
-      <c r="B15" s="41">
-        <v>21236.848947451224</v>
-      </c>
-      <c r="C15" s="42">
-        <v>1019756.7452947793</v>
-      </c>
-      <c r="D15" s="43">
-        <f>B15/C15*100</f>
-        <v>2.0825406691781505</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A16" s="40">
-        <v>2007</v>
-      </c>
-      <c r="B16" s="41">
-        <v>32394.037818461522</v>
-      </c>
-      <c r="C16" s="42">
-        <v>1102718.0446246397</v>
-      </c>
-      <c r="D16" s="43">
-        <f t="shared" ref="D16:D34" si="0">B16/C16*100</f>
-        <v>2.9376537344583227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A17" s="40">
-        <v>2008</v>
-      </c>
-      <c r="B17" s="41">
-        <v>29521.419070842763</v>
-      </c>
-      <c r="C17" s="42">
-        <v>1170112.7184744328</v>
-      </c>
-      <c r="D17" s="43">
-        <f t="shared" si="0"/>
-        <v>2.5229551482298338</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A18" s="40">
-        <v>2009</v>
-      </c>
-      <c r="B18" s="41">
-        <v>17851.259975357607</v>
-      </c>
-      <c r="C18" s="42">
-        <v>946314.39199439762</v>
-      </c>
-      <c r="D18" s="43">
-        <f t="shared" si="0"/>
-        <v>1.8863984449962048</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A19" s="40">
-        <v>2010</v>
-      </c>
-      <c r="B19" s="41">
-        <v>27199.001574955291</v>
-      </c>
-      <c r="C19" s="42">
-        <v>1106477.9522027229</v>
-      </c>
-      <c r="D19" s="43">
-        <f t="shared" si="0"/>
-        <v>2.4581602842432453</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A20" s="40">
-        <v>2011</v>
-      </c>
-      <c r="B20" s="41">
-        <v>25632.564790888606</v>
-      </c>
-      <c r="C20" s="42">
-        <v>1229155.9189018873</v>
-      </c>
-      <c r="D20" s="43">
-        <f t="shared" si="0"/>
-        <v>2.0853794377680273</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A21" s="40">
-        <v>2012</v>
-      </c>
-      <c r="B21" s="41">
-        <v>21769.332132260963</v>
-      </c>
-      <c r="C21" s="42">
-        <v>1255666.3354948985</v>
-      </c>
-      <c r="D21" s="43">
-        <f t="shared" si="0"/>
-        <v>1.7336876459048312</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A22" s="40">
-        <v>2013</v>
-      </c>
-      <c r="B22" s="41">
-        <v>48356.760011782091</v>
-      </c>
-      <c r="C22" s="42">
-        <v>1327866.0507596827</v>
-      </c>
-      <c r="D22" s="43">
-        <f t="shared" si="0"/>
-        <v>3.6416896104932275</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A23" s="40">
-        <v>2014</v>
-      </c>
-      <c r="B23" s="41">
-        <v>30351.497115624894</v>
-      </c>
-      <c r="C23" s="42">
-        <v>1363622.6805175482</v>
-      </c>
-      <c r="D23" s="43">
-        <f t="shared" si="0"/>
-        <v>2.2257987894499753</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A24" s="40">
-        <v>2015</v>
-      </c>
-      <c r="B24" s="41">
-        <v>35945.172957005554</v>
-      </c>
-      <c r="C24" s="42">
-        <v>1212930.7465036674</v>
-      </c>
-      <c r="D24" s="43">
-        <f t="shared" si="0"/>
-        <v>2.9634975500966796</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A25" s="40">
-        <v>2016</v>
-      </c>
-      <c r="B25" s="41">
-        <v>31192.304756424597</v>
-      </c>
-      <c r="C25" s="42">
-        <v>1110657.0604481746</v>
-      </c>
-      <c r="D25" s="43">
-        <f t="shared" si="0"/>
-        <v>2.8084550908844728</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A26" s="40">
-        <v>2017</v>
-      </c>
-      <c r="B26" s="41">
-        <v>34041.823482311593</v>
-      </c>
-      <c r="C26" s="42">
-        <v>1194607.8289517516</v>
-      </c>
-      <c r="D26" s="43">
-        <f t="shared" si="0"/>
-        <v>2.849623337240534</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A27" s="40">
-        <v>2018</v>
-      </c>
-      <c r="B27" s="41">
-        <v>34110.911240511574</v>
-      </c>
-      <c r="C27" s="42">
-        <v>1256815.2849659091</v>
-      </c>
-      <c r="D27" s="43">
-        <f t="shared" si="0"/>
-        <v>2.7140751428271201</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A28" s="40">
-        <v>2019</v>
-      </c>
-      <c r="B28" s="41">
-        <v>34619.748358263721</v>
-      </c>
-      <c r="C28" s="42">
-        <v>1304694.4748193177</v>
-      </c>
-      <c r="D28" s="43">
-        <f t="shared" si="0"/>
-        <v>2.6534755091269995</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A29" s="40">
-        <v>2020</v>
-      </c>
-      <c r="B29" s="41">
-        <v>28215.286421661629</v>
-      </c>
-      <c r="C29" s="42">
-        <v>1129590.1133632597</v>
-      </c>
-      <c r="D29" s="43">
-        <f t="shared" si="0"/>
-        <v>2.4978340450991543</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A30" s="40">
-        <v>2021</v>
-      </c>
-      <c r="B30" s="41">
-        <v>33847.015206203112</v>
-      </c>
-      <c r="C30" s="42">
-        <v>1315877.8466304687</v>
-      </c>
-      <c r="D30" s="43">
-        <f t="shared" si="0"/>
-        <v>2.572200397846518</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A31" s="39">
-        <v>2022</v>
-      </c>
-      <c r="B31" s="41">
-        <v>36419.45219572213</v>
-      </c>
-      <c r="C31" s="42">
-        <v>1468611.058063928</v>
-      </c>
-      <c r="D31" s="43">
-        <f t="shared" si="0"/>
-        <v>2.4798568685526541</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A32" s="40">
-        <v>2023</v>
-      </c>
-      <c r="B32" s="41">
-        <v>36475.534208166027</v>
-      </c>
-      <c r="C32" s="42">
-        <v>1799650.8987576375</v>
-      </c>
-      <c r="D32" s="43">
-        <f t="shared" si="0"/>
-        <v>2.0268116573801271</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A33" s="39">
-        <v>2024</v>
-      </c>
-      <c r="B33" s="41">
-        <v>37934.702450024553</v>
-      </c>
-      <c r="C33" s="42">
-        <v>1834690.0529423493</v>
-      </c>
-      <c r="D33" s="43">
-        <f t="shared" si="0"/>
-        <v>2.0676354782208306</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A34" s="59">
-        <v>2025</v>
-      </c>
-      <c r="B34" s="44">
-        <v>40870.76932803377</v>
-      </c>
-      <c r="C34" s="58">
-        <v>1839546.8691226</v>
-      </c>
-      <c r="D34" s="62">
-        <f t="shared" si="0"/>
-        <v>2.2217846152257978</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-    </row>
-    <row r="36" spans="1:11" s="39" customFormat="1" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A36" s="30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="17.25" x14ac:dyDescent="0.6">
-      <c r="A37" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="63"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="63"/>
-      <c r="K38" s="63"/>
-    </row>
-    <row r="39" spans="1:11" ht="17.25" x14ac:dyDescent="0.6"/>
-    <row r="40" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.6"/>
-    <row r="41" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.6"/>
-    <row r="42" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.6"/>
-    <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.6"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" ht="44.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="74"/>
+      <c r="K37" s="74"/>
+    </row>
+    <row r="38" spans="1:11" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+    </row>
+    <row r="39" spans="1:11" ht="19.8" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="40" spans="1:11" ht="19.8" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="41" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="42" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="44" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:V3"/>
-    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5760,216 +5784,78 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I73"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I63"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="11.4" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="11.3828125" customWidth="1"/>
-    <col min="10" max="11" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="12" max="256" width="11.3828125" hidden="1"/>
-    <col min="257" max="267" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="268" max="512" width="11.3828125" hidden="1"/>
-    <col min="513" max="523" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="524" max="768" width="11.3828125" hidden="1"/>
-    <col min="769" max="779" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="780" max="1024" width="11.3828125" hidden="1"/>
-    <col min="1025" max="1035" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="1036" max="1280" width="11.3828125" hidden="1"/>
-    <col min="1281" max="1291" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="1292" max="1536" width="11.3828125" hidden="1"/>
-    <col min="1537" max="1547" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="1548" max="1792" width="11.3828125" hidden="1"/>
-    <col min="1793" max="1803" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="1804" max="2048" width="11.3828125" hidden="1"/>
-    <col min="2049" max="2059" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="2060" max="2304" width="11.3828125" hidden="1"/>
-    <col min="2305" max="2315" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="2316" max="2560" width="11.3828125" hidden="1"/>
-    <col min="2561" max="2571" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="2572" max="2816" width="11.3828125" hidden="1"/>
-    <col min="2817" max="2827" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="2828" max="3072" width="11.3828125" hidden="1"/>
-    <col min="3073" max="3083" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="3084" max="3328" width="11.3828125" hidden="1"/>
-    <col min="3329" max="3339" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="3340" max="3584" width="11.3828125" hidden="1"/>
-    <col min="3585" max="3595" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="3596" max="3840" width="11.3828125" hidden="1"/>
-    <col min="3841" max="3851" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="3852" max="4096" width="11.3828125" hidden="1"/>
-    <col min="4097" max="4107" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="4108" max="4352" width="11.3828125" hidden="1"/>
-    <col min="4353" max="4363" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="4364" max="4608" width="11.3828125" hidden="1"/>
-    <col min="4609" max="4619" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="4620" max="4864" width="11.3828125" hidden="1"/>
-    <col min="4865" max="4875" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="4876" max="5120" width="11.3828125" hidden="1"/>
-    <col min="5121" max="5131" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="5132" max="5376" width="11.3828125" hidden="1"/>
-    <col min="5377" max="5387" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="5388" max="5632" width="11.3828125" hidden="1"/>
-    <col min="5633" max="5643" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="5644" max="5888" width="11.3828125" hidden="1"/>
-    <col min="5889" max="5899" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="5900" max="6144" width="11.3828125" hidden="1"/>
-    <col min="6145" max="6155" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="6156" max="6400" width="11.3828125" hidden="1"/>
-    <col min="6401" max="6411" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="6412" max="6656" width="11.3828125" hidden="1"/>
-    <col min="6657" max="6667" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="6668" max="6912" width="11.3828125" hidden="1"/>
-    <col min="6913" max="6923" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="6924" max="7168" width="11.3828125" hidden="1"/>
-    <col min="7169" max="7179" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="7180" max="7424" width="11.3828125" hidden="1"/>
-    <col min="7425" max="7435" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="7436" max="7680" width="11.3828125" hidden="1"/>
-    <col min="7681" max="7691" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="7692" max="7936" width="11.3828125" hidden="1"/>
-    <col min="7937" max="7947" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="7948" max="8192" width="11.3828125" hidden="1"/>
-    <col min="8193" max="8203" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="8204" max="8448" width="11.3828125" hidden="1"/>
-    <col min="8449" max="8459" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="8460" max="8704" width="11.3828125" hidden="1"/>
-    <col min="8705" max="8715" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="8716" max="8960" width="11.3828125" hidden="1"/>
-    <col min="8961" max="8971" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="8972" max="9216" width="11.3828125" hidden="1"/>
-    <col min="9217" max="9227" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="9228" max="9472" width="11.3828125" hidden="1"/>
-    <col min="9473" max="9483" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="9484" max="9728" width="11.3828125" hidden="1"/>
-    <col min="9729" max="9739" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="9740" max="9984" width="11.3828125" hidden="1"/>
-    <col min="9985" max="9995" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="9996" max="10240" width="11.3828125" hidden="1"/>
-    <col min="10241" max="10251" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="10252" max="10496" width="11.3828125" hidden="1"/>
-    <col min="10497" max="10507" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="10508" max="10752" width="11.3828125" hidden="1"/>
-    <col min="10753" max="10763" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="10764" max="11008" width="11.3828125" hidden="1"/>
-    <col min="11009" max="11019" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="11020" max="11264" width="11.3828125" hidden="1"/>
-    <col min="11265" max="11275" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="11276" max="11520" width="11.3828125" hidden="1"/>
-    <col min="11521" max="11531" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="11532" max="11776" width="11.3828125" hidden="1"/>
-    <col min="11777" max="11787" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="11788" max="12032" width="11.3828125" hidden="1"/>
-    <col min="12033" max="12043" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="12044" max="12288" width="11.3828125" hidden="1"/>
-    <col min="12289" max="12299" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="12300" max="12544" width="11.3828125" hidden="1"/>
-    <col min="12545" max="12555" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="12556" max="12800" width="11.3828125" hidden="1"/>
-    <col min="12801" max="12811" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="12812" max="13056" width="11.3828125" hidden="1"/>
-    <col min="13057" max="13067" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="13068" max="13312" width="11.3828125" hidden="1"/>
-    <col min="13313" max="13323" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="13324" max="13568" width="11.3828125" hidden="1"/>
-    <col min="13569" max="13579" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="13580" max="13824" width="11.3828125" hidden="1"/>
-    <col min="13825" max="13835" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="13836" max="14080" width="11.3828125" hidden="1"/>
-    <col min="14081" max="14091" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="14092" max="14336" width="11.3828125" hidden="1"/>
-    <col min="14337" max="14347" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="14348" max="14592" width="11.3828125" hidden="1"/>
-    <col min="14593" max="14603" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="14604" max="14848" width="11.3828125" hidden="1"/>
-    <col min="14849" max="14859" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="14860" max="15104" width="11.3828125" hidden="1"/>
-    <col min="15105" max="15115" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="15116" max="15360" width="11.3828125" hidden="1"/>
-    <col min="15361" max="15371" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="15372" max="15616" width="11.3828125" hidden="1"/>
-    <col min="15617" max="15627" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="15628" max="15872" width="11.3828125" hidden="1"/>
-    <col min="15873" max="15883" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="15884" max="16128" width="11.3828125" hidden="1"/>
-    <col min="16129" max="16139" width="11.3828125" hidden="1" customWidth="1"/>
-    <col min="16140" max="16384" width="11.3828125" hidden="1"/>
+    <col min="1" max="9" width="11.375" customWidth="1"/>
+    <col min="10" max="16384" width="11.375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="2" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="3" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="4" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="5" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="6" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="7" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="8" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="9" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="10" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="11" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="12" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="13" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="14" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="15" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="16" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="11.65" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1" x14ac:dyDescent="0.2"/>
+    <row r="2" x14ac:dyDescent="0.2"/>
+    <row r="3" x14ac:dyDescent="0.2"/>
+    <row r="4" x14ac:dyDescent="0.2"/>
+    <row r="5" x14ac:dyDescent="0.2"/>
+    <row r="6" x14ac:dyDescent="0.2"/>
+    <row r="7" x14ac:dyDescent="0.2"/>
+    <row r="8" x14ac:dyDescent="0.2"/>
+    <row r="9" x14ac:dyDescent="0.2"/>
+    <row r="10" x14ac:dyDescent="0.2"/>
+    <row r="11" x14ac:dyDescent="0.2"/>
+    <row r="12" x14ac:dyDescent="0.2"/>
+    <row r="13" x14ac:dyDescent="0.2"/>
+    <row r="14" x14ac:dyDescent="0.2"/>
+    <row r="15" x14ac:dyDescent="0.2"/>
+    <row r="16" x14ac:dyDescent="0.2"/>
+    <row r="17" x14ac:dyDescent="0.2"/>
+    <row r="18" x14ac:dyDescent="0.2"/>
+    <row r="19" x14ac:dyDescent="0.2"/>
+    <row r="20" x14ac:dyDescent="0.2"/>
+    <row r="21" x14ac:dyDescent="0.2"/>
+    <row r="22" x14ac:dyDescent="0.2"/>
+    <row r="23" x14ac:dyDescent="0.2"/>
+    <row r="24" x14ac:dyDescent="0.2"/>
+    <row r="25" x14ac:dyDescent="0.2"/>
+    <row r="26" x14ac:dyDescent="0.2"/>
+    <row r="27" x14ac:dyDescent="0.2"/>
+    <row r="28" x14ac:dyDescent="0.2"/>
+    <row r="29" x14ac:dyDescent="0.2"/>
+    <row r="30" x14ac:dyDescent="0.2"/>
+    <row r="31" x14ac:dyDescent="0.2"/>
+    <row r="32" x14ac:dyDescent="0.2"/>
+    <row r="33" x14ac:dyDescent="0.2"/>
+    <row r="34" x14ac:dyDescent="0.2"/>
+    <row r="35" x14ac:dyDescent="0.2"/>
+    <row r="36" x14ac:dyDescent="0.2"/>
+    <row r="37" x14ac:dyDescent="0.2"/>
+    <row r="38" x14ac:dyDescent="0.2"/>
+    <row r="39" x14ac:dyDescent="0.2"/>
+    <row r="40" x14ac:dyDescent="0.2"/>
+    <row r="41" x14ac:dyDescent="0.2"/>
+    <row r="42" x14ac:dyDescent="0.2"/>
+    <row r="43" x14ac:dyDescent="0.2"/>
+    <row r="44" x14ac:dyDescent="0.2"/>
+    <row r="45" x14ac:dyDescent="0.2"/>
+    <row r="46" x14ac:dyDescent="0.2"/>
+    <row r="47" x14ac:dyDescent="0.2"/>
+    <row r="48" x14ac:dyDescent="0.2"/>
+    <row r="49" x14ac:dyDescent="0.2"/>
+    <row r="50" x14ac:dyDescent="0.2"/>
+    <row r="51" x14ac:dyDescent="0.2"/>
+    <row r="52" x14ac:dyDescent="0.2"/>
+    <row r="53" x14ac:dyDescent="0.2"/>
+    <row r="54" x14ac:dyDescent="0.2"/>
+    <row r="55" x14ac:dyDescent="0.2"/>
+    <row r="56" x14ac:dyDescent="0.2"/>
+    <row r="57" x14ac:dyDescent="0.2"/>
+    <row r="58" x14ac:dyDescent="0.2"/>
+    <row r="59" x14ac:dyDescent="0.2"/>
+    <row r="60" x14ac:dyDescent="0.2"/>
+    <row r="61" x14ac:dyDescent="0.2"/>
+    <row r="62" x14ac:dyDescent="0.2"/>
+    <row r="63" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>